--- a/external_ids.xlsx
+++ b/external_ids.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,7 +438,3164 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1230663762</t>
+          <t>202510131418319</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2025101314461144</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025101316403950</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2025101316481658</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2025101318254762</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2025101321021199</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2025101406270674</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2025101407265069</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2025101408104771</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2025101408121387</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2025101408540327</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025101410235058</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025101412032674</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2025101412115248</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025101412211128</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025101413174990</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025101413195275</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025101413244449</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025101413575545</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025101413595082</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025101414113310</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>202510141412482</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2025101415232637</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2025101417524468</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2025101506131452</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2025101506464954</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2025101509211377</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2025101510092884</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2025101510563426</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2025101511173852</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2025101513055476</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2025101513082590</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2025101513093950</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2025101513114883</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2025101513184030</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2025101513554829</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2025101514022026</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2025101514042449</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2025101514254487</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2025101514491479</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>202510151452529</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2025101514574660</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2025101515083977</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2025101515202333</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>202510151526295</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2025101515494711</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2025101515583848</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2025101516003714</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2025101516085368</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2025101517554465</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2025101606414673</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2025101606473846</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2025101606500523</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2025101610062287</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2025101610130448</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2025101610183271</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2025101610215928</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2025101610385176</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>202510161041376</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2025101610432618</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2025101610453586</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2025101610473940</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2025101611002182</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2025101611165187</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2025101611281288</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2025101611364551</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2025101611404575</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2025101612463883</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2025101613023995</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2025101613043111</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2025101613061836</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2025101613075775</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2025101613090196</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2025101614125329</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2025101615350088</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2025101615390869</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2025101615433753</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2025101615542237</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2025101615591549</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2025101616031824</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2025101616103367</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2025101616174731</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2025101616353821</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2025101617062197</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2025101617121726</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2025101617163326</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2025101617184016</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2025101617240279</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2025101617264350</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2025101617264585</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2025101617303411</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2025101617324535</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2025101617341470</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2025101617345435</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2025101617371940</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2025101617385732</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2025101617392861</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2025101617423196</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2025101617450153</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>202510161755316</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2025101618024474</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2025101618101443</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2025101618341780</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2025101618473337</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2025101619284689</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2025101619323711</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2025101620532273</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2025101705534529</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>202510170559185</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2025101706213298</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2025101706270233</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2025101706312839</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2025101706340324</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2025101706343662</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2025101706374489</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2025101706461540</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2025101707025260</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2025101707090988</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>202510170727035</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2025101707403133</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2025101708200675</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2025101708223570</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2025101709383224</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2025101709431981</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2025101709520225</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2025101710065721</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2025101710122715</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2025101710173937</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2025101710350874</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2025101710401276</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2025101710433984</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2025101710475447</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2025101710484542</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2025101711041284</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>202510171110048</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2025101711123979</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2025101711124796</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2025101711175246</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2025101711214696</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2025101711251494</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2025101711303531</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2025101711422391</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2025101711425614</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2025101711463935</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2025101711535186</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2025101712365762</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2025101712440068</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2025101712485710</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2025101712500093</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2025101712540476</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2025101712554542</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2025101713051042</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2025101713090172</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2025101713192355</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2025101713241316</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2025101713283279</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2025101713311062</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2025101713383865</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2025101713422064</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2025101713450028</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2025101713474227</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2025101714004845</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2025101714023377</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2025101714043691</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2025101714084746</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2025101714111564</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>202510171413262</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2025101714160712</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2025101714175974</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2025101714205912</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2025101715002136</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2025101716130688</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2025101716414676</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2025101804005172</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2025101804021278</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2025101804043888</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2025101804060712</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2025101804074071</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2025101804091393</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2025101804104845</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2025101806071047</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2025101806372691</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2025101809082478</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2025101810244119</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2025101810270520</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2025101810292669</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2025101810314026</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2025101810335837</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2025101810472744</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2025101812301143</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2025101812330654</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2025101812370624</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2025101812401240</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2025101812463717</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>202510181349347</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2025101813514140</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>202510181354186</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2025101814220694</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2025101814324157</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2025101814350580</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>202510181439575</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>202510181442184</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2025101820242468</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2025101905242659</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2025101905272461</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2025101906160187</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2025101906195964</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2025101906522345</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2025101908174973</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2025101914470549</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2025101914492938</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2025101914523267</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2025101914550545</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2025101914583883</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>202510191500335</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2025102002402541</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2025102002493514</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2025102006203389</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2025102006245935</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2025102007060517</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2025102009381722</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>202510200940301</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2025102010091624</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2025102010103949</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2025102010111073</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2025102010124654</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2025102010144562</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2025102010151675</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2025102010162195</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2025102010173741</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2025102010183296</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2025102010213279</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2025102010221357</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2025102010234439</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2025102010275162</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2025102010301674</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2025102010323852</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2025102010345353</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2025102010583550</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>202510201059509</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2025102011011040</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2025102011024073</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2025102011092743</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2025102011112869</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2025102011131468</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2025102011144671</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2025102011152521</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2025102011162781</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2025102011173560</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2025102011194588</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2025102011252683</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2025102011373318</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2025102011392196</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2025102012594484</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2025102013021342</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2025102013153965</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2025102013183094</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2025102013214960</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2025102013215982</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2025102013233825</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2025102013253750</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2025102013280035</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2025102013284153</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2025102013294221</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2025102013312781</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2025102013404285</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2025102013432252</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2025102013445950</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2025102013480681</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2025102013555424</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>202510201405558</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2025102014103238</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2025102014125037</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2025102014151419</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2025102014171749</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2025102014251037</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2025102014303890</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2025102014381255</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2025102014550011</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2025102015052827</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2025102015173951</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2025102015211112</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2025102015221635</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2025102015235185</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2025102015242652</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2025102015255420</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2025102015274165</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>20251020152952100</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>202510201540133</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2025102015511750</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2025102015575280</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2025102016540094</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2025102018125713</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2025102019143914</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2025102019193214</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2025102019343616</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2025102019365337</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2025102022205669</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2025102104504368</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2025102104571163</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2025102106182779</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2025102107404310</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2025102108170545</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2025102108211531</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2025102108222036</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2025102108342939</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2025102108371878</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2025102108415532</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>202510210848185</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2025102108500228</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2025102108575386</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2025102109013974</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2025102109035625</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2025102109103157</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2025102109390487</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2025102109423163</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2025102109512342</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2025102109531478</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2025102109563122</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2025102109570641</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>202510210958097</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2025102110215420</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2025102110230380</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2025102110251945</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2025102110255667</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2025102110351630</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2025102111053422</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2025102111571822</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2025102112342962</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2025102112360864</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2025102112401386</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2025102112423122</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2025102112490069</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2025102113040417</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2025102114235016</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2025102114262422</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2025102121042457</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2025102121101914</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2025102121134483</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2025102121171554</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2025102121201498</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2025102121230475</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2025102202352717</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2025102202372732</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2025102205323193</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2025102206112043</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2025102206122483</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>202510220613591</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2025102206161925</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2025102206175989</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2025102206190973</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2025102206201146</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2025102206220196</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2025102206225853</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2025102207095317</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2025102207363186</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2025101406585259</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2025101407255513</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2025101408331646</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>202510140837082</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2025101410302595</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2025101413230729</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2025101415423717</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2025101415455136</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2025101610431879</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2025101610545559</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2025101613201515</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2025101613441468</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2025101706174766</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2025101706193313</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2025101706292781</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2025101707025875</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2025101707545456</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2025101708021640</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>20251017090105100</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2025101709404140</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2025101709494860</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2025101709544064</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2025101711060492</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2025101713124149</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2025101713243991</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2025101715105085</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2025101809233974</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>202510190140058</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2025101909183092</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2025101909203532</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2025101909221210</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2025101909241336</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2025101912274970</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2025101912373439</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2025101912463447</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2025102002274096</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2025102002370444</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2025102002432069</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2025102002583199</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2025102006521780</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2025102009225884</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>202510201017446</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2025102010194612</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2025102010212365</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2025102011040997</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2025102011401782</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2025102011412091</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2025102012133615</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2025102012180371</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2025102012264023</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2025102012325952</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2025102012381688</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2025102013045991</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2025102013521940</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2025102013594044</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>202510201408242</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2025102014273517</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2025102016144246</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2025102016195647</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2025102016235630</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2025102018140546</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2025102018432964</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2025102102275226</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2025102102304330</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2025102102370965</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2025102110222290</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2025102110291897</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2025102110454393</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>202510211109051</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2025102111212126</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2025102112214180</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2025102114032986</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2025102114122217</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2025102114165387</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2025102117131833</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2025102117155584</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2025102117292127</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2025102202234629</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2025102202273813</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2025102202313912</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2025102202332932</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>202510220630592</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2025102206322270</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2025102206594629</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2025102207184638</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2025101710505551</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2025102013165227</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2025102109284224</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2025110312073965</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2025110312105825</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>202511031215393</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2025110413325242</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2025111110280188</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2025111114394094</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>202511131545185</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2025111316101949</t>
         </is>
       </c>
     </row>
